--- a/nr-add-xslx/ig/StructureDefinition-NoteLiaison.xlsx
+++ b/nr-add-xslx/ig/StructureDefinition-NoteLiaison.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:15:44+00:00</t>
+    <t>2026-04-17T11:46:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-xslx/ig/StructureDefinition-NoteLiaison.xlsx
+++ b/nr-add-xslx/ig/StructureDefinition-NoteLiaison.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:46:18+00:00</t>
+    <t>2026-04-17T12:07:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
